--- a/uploads/CALCULADORA_V2.xlsx
+++ b/uploads/CALCULADORA_V2.xlsx
@@ -5009,7 +5009,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="B3" t="str">
         <v>ALUMNOS DE CICLO I</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="B3" t="str">
         <v>ALUMNOS TOTALES</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="B3" t="str">
         <v>ALUMNOS TOTALES</v>

--- a/uploads/CALCULADORA_V2.xlsx
+++ b/uploads/CALCULADORA_V2.xlsx
@@ -5849,7 +5849,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="B3" t="str">
         <v>ALUMNOS TOTALES</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="B3" t="str">
         <v>ALUMNOS TOTALES</v>
